--- a/Practical3/Excel Sheets/Task 2.xlsx
+++ b/Practical3/Excel Sheets/Task 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/bhwkau001_myuct_ac_za/Documents/Y3S2/Embedded2/Prac 3/Excel Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{30D031C4-E373-431F-B5C6-442A36ADBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA1481B7-7A08-429A-B3FD-1D3F110E959A}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{30D031C4-E373-431F-B5C6-442A36ADBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A858B66-F47E-4922-ACBA-13748E8B7D84}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{2A54ABB7-4433-4224-88CA-BB3349527BB3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A54ABB7-4433-4224-88CA-BB3349527BB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
   <si>
     <t>Exe_time</t>
   </si>
@@ -54,6 +54,15 @@
   </si>
   <si>
     <t>Fixed Point</t>
+  </si>
+  <si>
+    <t>Power Consumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current </t>
+  </si>
+  <si>
+    <t>Voltage</t>
   </si>
 </sst>
 </file>
@@ -154,33 +163,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,637 +525,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E974B9A-987C-47CD-A3B0-4413278F5F3A}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.21875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="9.44140625" customWidth="1"/>
-    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="1">
         <v>100</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="4">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="8">
         <v>250</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="4">
+      <c r="I1" s="8"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="8">
         <v>500</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="4">
+      <c r="L1" s="8"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="8">
         <v>750</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="5">
+      <c r="O1" s="8"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="2">
         <v>1000</v>
       </c>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+      <c r="R1" s="2"/>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="6"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2">
+      <c r="T2">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="U2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1">
         <v>128</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>2653</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>429384</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2">
+      <c r="F3" s="1">
+        <f>$T$2*$U$2*(D3/36000000)</f>
+        <v>8.9980916666666644E-6</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
         <v>5916</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="1">
         <v>968444</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1">
         <v>11296</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="1">
         <v>1857698</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1">
         <v>16660</v>
       </c>
-      <c r="N3" s="2">
+      <c r="O3" s="1">
         <v>2744850</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1">
         <v>22019</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="1">
         <v>3631126</v>
       </c>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2">
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
         <v>160</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>4241</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>669829</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F17" si="0">$T$2*$U$2*(D4/36000000)</f>
+        <v>1.4384058333333332E-5</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
         <v>9327</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="1">
         <v>1509977</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="J4" s="1"/>
+      <c r="K4" s="1">
         <v>17727</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="1">
         <v>2898149</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1">
         <v>26087</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="1">
         <v>4280853</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2">
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1">
         <v>34430</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="1">
         <v>5661611</v>
       </c>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2">
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1">
         <v>192</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>6097</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>966024</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>2.0678991666666665E-5</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>13447</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="1">
         <v>2179882</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="J5" s="1"/>
+      <c r="K5" s="1">
         <v>25572</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="1">
         <v>4182966</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1">
         <v>37660</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="1">
         <v>6180580</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
         <v>49735</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="1">
         <v>8176148</v>
       </c>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1">
         <v>224</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>8162</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>1314999</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2">
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7682783333333332E-5</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>18142</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="1">
         <v>2963391</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="J6" s="1"/>
+      <c r="K6" s="1">
         <v>34593</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="1">
         <v>5683767</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
         <v>51009</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="1">
         <v>8399191</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1">
         <v>67413</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="1">
         <v>11112491</v>
       </c>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8">
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
         <v>256</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="4">
         <v>10625</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="4">
         <v>1715812</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8">
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>3.6036458333333328E-5</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>23726</v>
       </c>
-      <c r="H7" s="8">
+      <c r="I7" s="4">
         <v>3873086</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4">
         <v>45358</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="4">
         <v>7437312</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8">
+      <c r="M7" s="4"/>
+      <c r="N7" s="4">
         <v>66915</v>
       </c>
-      <c r="N7" s="8">
+      <c r="O7" s="4">
         <v>10988990</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8">
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4">
         <v>88429</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="R7" s="4">
         <v>14534966</v>
       </c>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="6">
         <v>100</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="14">
+      <c r="E10" s="6"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="12">
         <v>250</v>
       </c>
-      <c r="H10" s="14"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="14">
+      <c r="J10" s="6"/>
+      <c r="K10" s="12">
         <v>500</v>
       </c>
-      <c r="K10" s="14"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="14">
+      <c r="M10" s="6"/>
+      <c r="N10" s="12">
         <v>750</v>
       </c>
-      <c r="N10" s="14"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="15">
+      <c r="P10" s="6"/>
+      <c r="Q10" s="7">
         <v>1000</v>
       </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="6"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="2" t="s">
+      <c r="R10" s="7"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2">
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
         <v>128</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>298</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>429524</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2">
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>1.0107166666666666E-6</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>550</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="1">
         <v>968356</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2">
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
         <v>964</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="1">
         <v>1857706</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1">
         <v>1378</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="1">
         <v>2744768</v>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2">
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1">
         <v>1790</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="1">
         <v>3630278</v>
       </c>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2">
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1">
         <v>160</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>574</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>670351</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2">
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9468166666666664E-6</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
         <v>966</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="1">
         <v>1511843</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
         <v>1614</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="1">
         <v>2900798</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1">
         <v>2258</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="1">
         <v>4284008</v>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2">
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1">
         <v>2902</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="1">
         <v>5665215</v>
       </c>
-      <c r="R13" s="6"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2">
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
         <v>192</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>807</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>966487</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2">
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
+        <v>2.737075E-6</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
         <v>1373</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="1">
         <v>2181412</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2">
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
         <v>2309</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="1">
         <v>4187949</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1">
         <v>3241</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="1">
         <v>6187996</v>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2">
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1">
         <v>4173</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14" s="1">
         <v>8185523</v>
       </c>
-      <c r="R14" s="6"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2">
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1">
         <v>224</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>956</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>1315375</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2">
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>3.2424333333333331E-6</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
         <v>1725</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="1">
         <v>2965173</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
         <v>2996</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="1">
         <v>5690483</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1">
         <v>4262</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="1">
         <v>8406389</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2">
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1">
         <v>5527</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="1">
         <v>11119849</v>
       </c>
-      <c r="R15" s="6"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2">
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1">
         <v>256</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>195</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>1716163</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2">
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>6.6137499999999998E-7</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
         <v>2201</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="1">
         <v>3873135</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
         <v>3861</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="1">
         <v>7434495</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1">
         <v>5518</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="1">
         <v>10987723</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2">
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1">
         <v>7172</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="1">
         <v>14535059</v>
       </c>
-      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A10:B11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Practical3/Excel Sheets/Task 2.xlsx
+++ b/Practical3/Excel Sheets/Task 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/Excel Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/bhwkau001_myuct_ac_za/Documents/Y3S2/Embedded2/Prac 3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{30D031C4-E373-431F-B5C6-442A36ADBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A858B66-F47E-4922-ACBA-13748E8B7D84}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{30D031C4-E373-431F-B5C6-442A36ADBE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07E92D1D-31BE-4C3F-ACD4-7F92D63DE698}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A54ABB7-4433-4224-88CA-BB3349527BB3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A54ABB7-4433-4224-88CA-BB3349527BB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
   <si>
     <t>Exe_time</t>
   </si>
@@ -54,15 +54,6 @@
   </si>
   <si>
     <t>Fixed Point</t>
-  </si>
-  <si>
-    <t>Power Consumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current </t>
-  </si>
-  <si>
-    <t>Voltage</t>
   </si>
 </sst>
 </file>
@@ -525,19 +516,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E974B9A-987C-47CD-A3B0-4413278F5F3A}">
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.21875" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="15" max="15" width="9.44140625" customWidth="1"/>
-    <col min="18" max="18" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
@@ -550,34 +540,27 @@
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="8">
+      <c r="G1" s="8">
         <v>250</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="8">
+      <c r="H1" s="8"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="8">
         <v>500</v>
       </c>
-      <c r="L1" s="8"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="8">
+      <c r="K1" s="8"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="8">
         <v>750</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2">
+      <c r="N1" s="8"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="2">
         <v>1000</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="1" t="s">
@@ -589,45 +572,36 @@
       <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="U2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1">
@@ -639,40 +613,36 @@
       <c r="E3" s="1">
         <v>429384</v>
       </c>
-      <c r="F3" s="1">
-        <f>$T$2*$U$2*(D3/36000000)</f>
-        <v>8.9980916666666644E-6</v>
-      </c>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>5916</v>
+      </c>
       <c r="H3" s="1">
-        <v>5916</v>
-      </c>
-      <c r="I3" s="1">
         <v>968444</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1">
+        <v>11296</v>
+      </c>
       <c r="K3" s="1">
-        <v>11296</v>
-      </c>
-      <c r="L3" s="1">
         <v>1857698</v>
       </c>
-      <c r="M3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1">
+        <v>16660</v>
+      </c>
       <c r="N3" s="1">
-        <v>16660</v>
-      </c>
-      <c r="O3" s="1">
         <v>2744850</v>
       </c>
-      <c r="P3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1">
+        <v>22019</v>
+      </c>
       <c r="Q3" s="1">
-        <v>22019</v>
-      </c>
-      <c r="R3" s="1">
         <v>3631126</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1">
@@ -684,40 +654,36 @@
       <c r="E4" s="1">
         <v>669829</v>
       </c>
-      <c r="F4" s="1">
-        <f t="shared" ref="F4:F17" si="0">$T$2*$U$2*(D4/36000000)</f>
-        <v>1.4384058333333332E-5</v>
-      </c>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>9327</v>
+      </c>
       <c r="H4" s="1">
-        <v>9327</v>
-      </c>
-      <c r="I4" s="1">
         <v>1509977</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>17727</v>
+      </c>
       <c r="K4" s="1">
-        <v>17727</v>
-      </c>
-      <c r="L4" s="1">
         <v>2898149</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1">
+        <v>26087</v>
+      </c>
       <c r="N4" s="1">
-        <v>26087</v>
-      </c>
-      <c r="O4" s="1">
         <v>4280853</v>
       </c>
-      <c r="P4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1">
+        <v>34430</v>
+      </c>
       <c r="Q4" s="1">
-        <v>34430</v>
-      </c>
-      <c r="R4" s="1">
         <v>5661611</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1">
@@ -729,40 +695,36 @@
       <c r="E5" s="1">
         <v>966024</v>
       </c>
-      <c r="F5" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0678991666666665E-5</v>
-      </c>
-      <c r="G5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
+        <v>13447</v>
+      </c>
       <c r="H5" s="1">
-        <v>13447</v>
-      </c>
-      <c r="I5" s="1">
         <v>2179882</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>25572</v>
+      </c>
       <c r="K5" s="1">
-        <v>25572</v>
-      </c>
-      <c r="L5" s="1">
         <v>4182966</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1">
+        <v>37660</v>
+      </c>
       <c r="N5" s="1">
-        <v>37660</v>
-      </c>
-      <c r="O5" s="1">
         <v>6180580</v>
       </c>
-      <c r="P5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1">
+        <v>49735</v>
+      </c>
       <c r="Q5" s="1">
-        <v>49735</v>
-      </c>
-      <c r="R5" s="1">
         <v>8176148</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1">
@@ -774,40 +736,36 @@
       <c r="E6" s="1">
         <v>1314999</v>
       </c>
-      <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7682783333333332E-5</v>
-      </c>
-      <c r="G6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>18142</v>
+      </c>
       <c r="H6" s="1">
-        <v>18142</v>
-      </c>
-      <c r="I6" s="1">
         <v>2963391</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
+        <v>34593</v>
+      </c>
       <c r="K6" s="1">
-        <v>34593</v>
-      </c>
-      <c r="L6" s="1">
         <v>5683767</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1">
+        <v>51009</v>
+      </c>
       <c r="N6" s="1">
-        <v>51009</v>
-      </c>
-      <c r="O6" s="1">
         <v>8399191</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1">
+        <v>67413</v>
+      </c>
       <c r="Q6" s="1">
-        <v>67413</v>
-      </c>
-      <c r="R6" s="1">
         <v>11112491</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4">
@@ -819,46 +777,42 @@
       <c r="E7" s="4">
         <v>1715812</v>
       </c>
-      <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6036458333333328E-5</v>
-      </c>
-      <c r="G7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
+        <v>23726</v>
+      </c>
       <c r="H7" s="4">
-        <v>23726</v>
-      </c>
-      <c r="I7" s="4">
         <v>3873086</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4">
+        <v>45358</v>
+      </c>
       <c r="K7" s="4">
-        <v>45358</v>
-      </c>
-      <c r="L7" s="4">
         <v>7437312</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
+        <v>66915</v>
+      </c>
       <c r="N7" s="4">
-        <v>66915</v>
-      </c>
-      <c r="O7" s="4">
         <v>10988990</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4">
+        <v>88429</v>
+      </c>
       <c r="Q7" s="4">
-        <v>88429</v>
-      </c>
-      <c r="R7" s="4">
         <v>14534966</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="1"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -870,15 +824,14 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -890,9 +843,8 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -904,29 +856,28 @@
         <v>100</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="12">
+      <c r="F10" s="6"/>
+      <c r="G10" s="12">
         <v>250</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="12">
+      <c r="H10" s="12"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="12">
         <v>500</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="12">
+      <c r="K10" s="12"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="12">
         <v>750</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="7">
+      <c r="N10" s="12"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="7">
         <v>1000</v>
       </c>
-      <c r="R10" s="7"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="1" t="s">
@@ -938,276 +889,250 @@
       <c r="E11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="H11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1"/>
+      <c r="M11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1"/>
+      <c r="P11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>128</v>
       </c>
       <c r="D12" s="1">
-        <v>298</v>
+        <v>388</v>
       </c>
       <c r="E12" s="1">
         <v>429524</v>
       </c>
-      <c r="F12" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0107166666666666E-6</v>
-      </c>
-      <c r="G12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <v>550</v>
+      </c>
       <c r="H12" s="1">
-        <v>550</v>
-      </c>
-      <c r="I12" s="1">
         <v>968356</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>964</v>
+      </c>
       <c r="K12" s="1">
-        <v>964</v>
-      </c>
-      <c r="L12" s="1">
         <v>1857706</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1">
+        <v>1378</v>
+      </c>
       <c r="N12" s="1">
-        <v>1378</v>
-      </c>
-      <c r="O12" s="1">
         <v>2744768</v>
       </c>
-      <c r="P12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>1790</v>
+      </c>
       <c r="Q12" s="1">
-        <v>1790</v>
-      </c>
-      <c r="R12" s="1">
         <v>3630278</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1">
         <v>160</v>
       </c>
       <c r="D13" s="1">
-        <v>574</v>
+        <v>714</v>
       </c>
       <c r="E13" s="1">
         <v>670351</v>
       </c>
-      <c r="F13" s="1">
-        <f t="shared" si="0"/>
-        <v>1.9468166666666664E-6</v>
-      </c>
-      <c r="G13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <v>966</v>
+      </c>
       <c r="H13" s="1">
-        <v>966</v>
-      </c>
-      <c r="I13" s="1">
         <v>1511843</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>1614</v>
+      </c>
       <c r="K13" s="1">
-        <v>1614</v>
-      </c>
-      <c r="L13" s="1">
         <v>2900798</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1">
+        <v>2258</v>
+      </c>
       <c r="N13" s="1">
-        <v>2258</v>
-      </c>
-      <c r="O13" s="1">
         <v>4284008</v>
       </c>
-      <c r="P13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>2902</v>
+      </c>
       <c r="Q13" s="1">
-        <v>2902</v>
-      </c>
-      <c r="R13" s="1">
         <v>5665215</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1">
         <v>192</v>
       </c>
       <c r="D14" s="1">
-        <v>807</v>
+        <v>1009</v>
       </c>
       <c r="E14" s="1">
         <v>966487</v>
       </c>
-      <c r="F14" s="1">
-        <f t="shared" si="0"/>
-        <v>2.737075E-6</v>
-      </c>
-      <c r="G14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <v>1373</v>
+      </c>
       <c r="H14" s="1">
-        <v>1373</v>
-      </c>
-      <c r="I14" s="1">
         <v>2181412</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>2309</v>
+      </c>
       <c r="K14" s="1">
-        <v>2309</v>
-      </c>
-      <c r="L14" s="1">
         <v>4187949</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1">
+        <v>3241</v>
+      </c>
       <c r="N14" s="1">
-        <v>3241</v>
-      </c>
-      <c r="O14" s="1">
         <v>6187996</v>
       </c>
-      <c r="P14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>4173</v>
+      </c>
       <c r="Q14" s="1">
-        <v>4173</v>
-      </c>
-      <c r="R14" s="1">
         <v>8185523</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1">
         <v>224</v>
       </c>
       <c r="D15" s="1">
-        <v>956</v>
+        <v>1231</v>
       </c>
       <c r="E15" s="1">
         <v>1315375</v>
       </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>3.2424333333333331E-6</v>
-      </c>
-      <c r="G15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
+        <v>1725</v>
+      </c>
       <c r="H15" s="1">
-        <v>1725</v>
-      </c>
-      <c r="I15" s="1">
         <v>2965173</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>2996</v>
+      </c>
       <c r="K15" s="1">
-        <v>2996</v>
-      </c>
-      <c r="L15" s="1">
         <v>5690483</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1">
+        <v>4262</v>
+      </c>
       <c r="N15" s="1">
-        <v>4262</v>
-      </c>
-      <c r="O15" s="1">
         <v>8406389</v>
       </c>
-      <c r="P15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>5527</v>
+      </c>
       <c r="Q15" s="1">
-        <v>5527</v>
-      </c>
-      <c r="R15" s="1">
         <v>11119849</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1">
         <v>256</v>
       </c>
       <c r="D16" s="1">
-        <v>195</v>
+        <v>1554</v>
       </c>
       <c r="E16" s="1">
         <v>1716163</v>
       </c>
-      <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>6.6137499999999998E-7</v>
-      </c>
-      <c r="G16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1">
+        <v>2201</v>
+      </c>
       <c r="H16" s="1">
-        <v>2201</v>
-      </c>
-      <c r="I16" s="1">
         <v>3873135</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>3861</v>
+      </c>
       <c r="K16" s="1">
-        <v>3861</v>
-      </c>
-      <c r="L16" s="1">
         <v>7434495</v>
       </c>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1">
+        <v>5518</v>
+      </c>
       <c r="N16" s="1">
-        <v>5518</v>
-      </c>
-      <c r="O16" s="1">
         <v>10987723</v>
       </c>
-      <c r="P16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>7172</v>
+      </c>
       <c r="Q16" s="1">
-        <v>7172</v>
-      </c>
-      <c r="R16" s="1">
         <v>14535059</v>
       </c>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M1:N1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A10:B11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
